--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:39</t>
+    <t xml:space="preserve">2026-09-09 22:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:25</t>
+    <t xml:space="preserve">2026-09-12 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:42</t>
+    <t xml:space="preserve">2026-09-24 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:19</t>
+    <t xml:space="preserve">2026-09-27 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:09</t>
+    <t xml:space="preserve">2026-09-29 11:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>29.5</v>
+        <v>295.03</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>23.46</v>
+        <v>234.55</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>21.57</v>
+        <v>215.7</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>21.11</v>
+        <v>211.07</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.66</v>
+        <v>196.61</v>
       </c>
     </row>
     <row r="7">
@@ -608,7 +608,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>18.67</v>
+        <v>186.66</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16.91</v>
+        <v>169.11</v>
       </c>
     </row>
     <row r="9">
@@ -642,7 +642,7 @@
         <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15.72</v>
+        <v>157.17</v>
       </c>
     </row>
     <row r="10">
@@ -659,7 +659,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14.7</v>
+        <v>146.99</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         <v>2024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14.7</v>
+        <v>146.98</v>
       </c>
     </row>
     <row r="12">
@@ -693,7 +693,7 @@
         <v>2024</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14.34</v>
+        <v>143.39</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
         <v>2024</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12.18</v>
+        <v>121.78</v>
       </c>
     </row>
     <row r="14">
@@ -727,7 +727,7 @@
         <v>2024</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10.67</v>
+        <v>106.75</v>
       </c>
     </row>
     <row r="15">
@@ -744,7 +744,7 @@
         <v>2024</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9.6</v>
+        <v>96.03</v>
       </c>
     </row>
     <row r="16">
@@ -761,7 +761,7 @@
         <v>2024</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9.46</v>
+        <v>94.64</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:03</t>
+    <t xml:space="preserve">2026-10-01 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:28</t>
+    <t xml:space="preserve">2026-10-02 13:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:01</t>
+    <t xml:space="preserve">2026-10-04 08:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2024_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:00</t>
+    <t xml:space="preserve">2026-10-05 07:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
